--- a/tests/fixtures/16_bundesliga/16_bundesliga_pattern-from-draft.xlsx
+++ b/tests/fixtures/16_bundesliga/16_bundesliga_pattern-from-draft.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -466,29 +466,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>read.direction</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pattern.version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -498,12 +490,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>read.direction</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Spielplan</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="D2" s="1" t="n"/>
@@ -516,33 +508,29 @@
       <c r="K2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>meta.source</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>.+</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>config:</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Spielplan</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -552,7 +540,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>meta.highlighted_club</t>
+          <t>meta.source</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -581,7 +569,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>meta.title</t>
+          <t>meta.highlighted_club</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -603,33 +591,33 @@
       <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>col_datum</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>meta.title</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>.+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -639,7 +627,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>col_spieltag</t>
+          <t>col_datum</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -649,7 +637,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Spieltag</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="E7" s="3" t="n"/>
@@ -668,7 +656,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>col_heim</t>
+          <t>col_spieltag</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -678,7 +666,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Heimmannschaft</t>
+          <t>Spieltag</t>
         </is>
       </c>
       <c r="E8" s="3" t="n"/>
@@ -697,7 +685,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>col_gast</t>
+          <t>col_heim</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -707,7 +695,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Gastmannschaft</t>
+          <t>Heimmannschaft</t>
         </is>
       </c>
       <c r="E9" s="3" t="n"/>
@@ -726,7 +714,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>col_split</t>
+          <t>col_gast</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -736,7 +724,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>split</t>
+          <t>Gastmannschaft</t>
         </is>
       </c>
       <c r="E10" s="3" t="n"/>
@@ -755,7 +743,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>col_win</t>
+          <t>col_split</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -765,7 +753,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>split</t>
         </is>
       </c>
       <c r="E11" s="3" t="n"/>
@@ -784,7 +772,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>col_draw</t>
+          <t>col_win</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -794,7 +782,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>win</t>
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
@@ -813,7 +801,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>col_defeat</t>
+          <t>col_draw</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -823,7 +811,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>defeat</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="E13" s="3" t="n"/>
@@ -842,7 +830,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>col_goals</t>
+          <t>col_defeat</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -852,7 +840,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>defeat</t>
         </is>
       </c>
       <c r="E14" s="3" t="n"/>
@@ -864,33 +852,33 @@
       <c r="K14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>match.datum</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>.+</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>col_goals</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>goals</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -900,17 +888,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>match.spieltag</t>
+          <t>match.datum</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.+</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
@@ -929,17 +917,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>match.home</t>
+          <t>match.spieltag</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>\d+</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -958,7 +946,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>match.away</t>
+          <t>match.home</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -987,17 +975,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>match.win</t>
+          <t>match.away</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.+</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -1016,7 +1004,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>match.draw</t>
+          <t>match.win</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1045,7 +1033,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>match.defeat</t>
+          <t>match.draw</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1074,17 +1062,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>match.goals</t>
+          <t>match.defeat</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>\d+:\d+</t>
+          <t>\d+</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -1096,52 +1084,60 @@
       <c r="K22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>match.goals</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>\d+:\d+</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>cell:A1</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>meta.source</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>cell:E1</t>
+          <t>cell:A1</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>meta.highlighted_club</t>
+          <t>meta.source</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -1157,12 +1153,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>cell:C2</t>
+          <t>cell:E1</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>meta.title</t>
+          <t>meta.highlighted_club</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -1176,144 +1172,165 @@
       <c r="K26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>cell:C2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>meta.title</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>col_datum</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>col_spieltag</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>col_heim</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>col_gast</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>col_split</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>col_win</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>col_draw</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>col_defeat</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>col_goals</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>match.datum</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>match.spieltag</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>match.home</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>match.away</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>match.win</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>match.draw</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>match.defeat</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>match.goals</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
